--- a/tabelas_formatadas.xlsx
+++ b/tabelas_formatadas.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alinsperedu-my.sharepoint.com/personal/mateuscc_al_insper_edu_br/Documents/Meu Drive/Insper/Insper Data/Projeto_1_CB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7D0B9996-2C12-4D7E-BD36-6F8ADD64B7E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{7D0B9996-2C12-4D7E-BD36-6F8ADD64B7E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82E7AE0D-48C3-4B0C-948F-1EAE09B9BE31}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Preço por Continente" sheetId="1" r:id="rId1"/>
     <sheet name="Conversão INR-USD" sheetId="2" r:id="rId2"/>
-    <sheet name="Mediana e Média" sheetId="3" r:id="rId3"/>
-    <sheet name="Studios por Continente" sheetId="4" r:id="rId4"/>
+    <sheet name="Planilha1" sheetId="5" r:id="rId3"/>
+    <sheet name="Mediana e Média" sheetId="3" r:id="rId4"/>
+    <sheet name="Studios por Continente" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="138">
   <si>
     <t>Preço por continente</t>
   </si>
@@ -434,6 +435,9 @@
   </si>
   <si>
     <t>$ 22.943,28</t>
+  </si>
+  <si>
+    <t>Taxa usada (INR por USD): 83,16</t>
   </si>
 </sst>
 </file>
@@ -445,7 +449,7 @@
     <numFmt numFmtId="8" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -526,6 +530,14 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -555,7 +567,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -587,12 +599,75 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -636,6 +711,20 @@
     <xf numFmtId="44" fontId="5" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -1335,6 +1424,536 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10EED913-B9F7-40C2-8A62-3BDF89D4E95C}">
+  <dimension ref="B3:L31"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B3" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="20">
+        <v>0.25</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" s="20">
+        <v>0.75</v>
+      </c>
+      <c r="J3" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B4" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="21">
+        <v>562</v>
+      </c>
+      <c r="D4" s="22">
+        <v>274.47000000000003</v>
+      </c>
+      <c r="E4" s="22">
+        <v>719.29</v>
+      </c>
+      <c r="F4" s="21">
+        <v>9.51</v>
+      </c>
+      <c r="G4" s="21">
+        <v>25.9</v>
+      </c>
+      <c r="H4" s="21">
+        <v>87.63</v>
+      </c>
+      <c r="I4" s="22">
+        <v>252.86</v>
+      </c>
+      <c r="J4" s="22">
+        <v>11520.9</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B5" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="21">
+        <v>49</v>
+      </c>
+      <c r="D5" s="21">
+        <v>389.12</v>
+      </c>
+      <c r="E5" s="22">
+        <v>895.03</v>
+      </c>
+      <c r="F5" s="21">
+        <v>12.13</v>
+      </c>
+      <c r="G5" s="21">
+        <v>49.3</v>
+      </c>
+      <c r="H5" s="21">
+        <v>120.14</v>
+      </c>
+      <c r="I5" s="22">
+        <v>241.46</v>
+      </c>
+      <c r="J5" s="22">
+        <v>5473.24</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B6" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="23">
+        <v>4844</v>
+      </c>
+      <c r="D6" s="22">
+        <v>268.91000000000003</v>
+      </c>
+      <c r="E6" s="22">
+        <v>608.57000000000005</v>
+      </c>
+      <c r="F6" s="21">
+        <v>10.77</v>
+      </c>
+      <c r="G6" s="22">
+        <v>86.42</v>
+      </c>
+      <c r="H6" s="22">
+        <v>131.11000000000001</v>
+      </c>
+      <c r="I6" s="22">
+        <v>239.06</v>
+      </c>
+      <c r="J6" s="22">
+        <v>14689.45</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B7" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="21">
+        <v>41</v>
+      </c>
+      <c r="D7" s="22">
+        <v>289.45999999999998</v>
+      </c>
+      <c r="E7" s="22">
+        <v>290.01</v>
+      </c>
+      <c r="F7" s="21">
+        <v>37.42</v>
+      </c>
+      <c r="G7" s="22">
+        <v>157.35</v>
+      </c>
+      <c r="H7" s="22">
+        <v>223.97</v>
+      </c>
+      <c r="I7" s="22">
+        <v>336.81</v>
+      </c>
+      <c r="J7" s="22">
+        <v>1855.03</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B8" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="21">
+        <v>579</v>
+      </c>
+      <c r="D8" s="21">
+        <v>150.1</v>
+      </c>
+      <c r="E8" s="22">
+        <v>493.88</v>
+      </c>
+      <c r="F8" s="21">
+        <v>9.84</v>
+      </c>
+      <c r="G8" s="21">
+        <v>36.049999999999997</v>
+      </c>
+      <c r="H8" s="21">
+        <v>67.34</v>
+      </c>
+      <c r="I8" s="21">
+        <v>144.61000000000001</v>
+      </c>
+      <c r="J8" s="22">
+        <v>10967.42</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B9" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="23">
+        <v>6688</v>
+      </c>
+      <c r="D9" s="22">
+        <v>168.4</v>
+      </c>
+      <c r="E9" s="22">
+        <v>473.56</v>
+      </c>
+      <c r="F9" s="21">
+        <v>4.7300000000000004</v>
+      </c>
+      <c r="G9" s="21">
+        <v>34.31</v>
+      </c>
+      <c r="H9" s="21">
+        <v>68.760000000000005</v>
+      </c>
+      <c r="I9" s="21">
+        <v>153.91999999999999</v>
+      </c>
+      <c r="J9" s="22">
+        <v>22943.279999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B13" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="C13" s="25"/>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="H15" s="19" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B16" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="23">
+        <v>12805</v>
+      </c>
+      <c r="H16" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="I16" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="J16" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="K16" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="L16" s="21" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B17" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="21">
+        <v>212.82</v>
+      </c>
+      <c r="H17" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="21">
+        <v>1</v>
+      </c>
+      <c r="J17" s="21">
+        <v>1</v>
+      </c>
+      <c r="K17" s="21">
+        <v>2</v>
+      </c>
+      <c r="L17" s="21">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B18" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="21">
+        <v>549.47</v>
+      </c>
+      <c r="H18" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I18" s="21">
+        <v>1</v>
+      </c>
+      <c r="J18" s="21">
+        <v>2</v>
+      </c>
+      <c r="K18" s="21">
+        <v>4</v>
+      </c>
+      <c r="L18" s="21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B19" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="21">
+        <v>4.7300000000000004</v>
+      </c>
+      <c r="H19" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="21">
+        <v>1</v>
+      </c>
+      <c r="J19" s="21">
+        <v>1</v>
+      </c>
+      <c r="K19" s="21">
+        <v>2</v>
+      </c>
+      <c r="L19" s="21">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B20" s="26">
+        <v>0.25</v>
+      </c>
+      <c r="C20" s="21">
+        <v>48.03</v>
+      </c>
+      <c r="H20" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="I20" s="21">
+        <v>1</v>
+      </c>
+      <c r="J20" s="21">
+        <v>1</v>
+      </c>
+      <c r="K20" s="21">
+        <v>2</v>
+      </c>
+      <c r="L20" s="21">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B21" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="21">
+        <v>98.3</v>
+      </c>
+      <c r="H21" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="I21" s="21">
+        <v>1</v>
+      </c>
+      <c r="J21" s="21">
+        <v>1</v>
+      </c>
+      <c r="K21" s="21">
+        <v>2</v>
+      </c>
+      <c r="L21" s="21">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B22" s="26">
+        <v>0.75</v>
+      </c>
+      <c r="C22" s="21">
+        <v>193.15</v>
+      </c>
+      <c r="H22" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="I22" s="21">
+        <v>1</v>
+      </c>
+      <c r="J22" s="21">
+        <v>1</v>
+      </c>
+      <c r="K22" s="21">
+        <v>2</v>
+      </c>
+      <c r="L22" s="21">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B23" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="22">
+        <v>22943.279999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="H24" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="27"/>
+      <c r="J24" s="27"/>
+      <c r="K24" s="27"/>
+      <c r="L24" s="27"/>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="H25" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="I25" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="J25" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="K25" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="L25" s="28" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="H26" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="I26" s="21">
+        <v>1.49</v>
+      </c>
+      <c r="J26" s="21">
+        <v>1.72</v>
+      </c>
+      <c r="K26" s="21">
+        <v>2.94</v>
+      </c>
+      <c r="L26" s="21">
+        <v>4.7699999999999996</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="H27" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I27" s="21">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="J27" s="21">
+        <v>2.29</v>
+      </c>
+      <c r="K27" s="21">
+        <v>4.41</v>
+      </c>
+      <c r="L27" s="21">
+        <v>6.47</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="H28" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="I28" s="21">
+        <v>1.7</v>
+      </c>
+      <c r="J28" s="21">
+        <v>2.09</v>
+      </c>
+      <c r="K28" s="21">
+        <v>3.33</v>
+      </c>
+      <c r="L28" s="21">
+        <v>5.04</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="H29" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="I29" s="21">
+        <v>1.22</v>
+      </c>
+      <c r="J29" s="21">
+        <v>1.8</v>
+      </c>
+      <c r="K29" s="21">
+        <v>2.59</v>
+      </c>
+      <c r="L29" s="21">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="H30" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="I30" s="21">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="J30" s="21">
+        <v>2.64</v>
+      </c>
+      <c r="K30" s="21">
+        <v>4.33</v>
+      </c>
+      <c r="L30" s="21">
+        <v>5.69</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="H31" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="I31" s="21">
+        <v>1.94</v>
+      </c>
+      <c r="J31" s="21">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="K31" s="21">
+        <v>2.99</v>
+      </c>
+      <c r="L31" s="21">
+        <v>5.28</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B13:C13"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1746,7 +2365,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
